--- a/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374_W0017F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.19786767053692</v>
+        <v>4.58215349646225</v>
       </c>
       <c r="D2" t="n">
-        <v>31.47888132908798</v>
+        <v>5.115318215976796</v>
       </c>
       <c r="E2" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F2" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.57188517851837</v>
+        <v>4.805431341509235</v>
       </c>
       <c r="D3" t="n">
-        <v>30.36345606857437</v>
+        <v>4.934061611143335</v>
       </c>
       <c r="E3" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F3" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.10435733585349</v>
+        <v>5.054458067076192</v>
       </c>
       <c r="D4" t="n">
-        <v>30.08922539097412</v>
+        <v>4.889499126033295</v>
       </c>
       <c r="E4" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F4" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.67367582742595</v>
+        <v>4.334472321956717</v>
       </c>
       <c r="D5" t="n">
-        <v>20.13565108071861</v>
+        <v>3.272043300616774</v>
       </c>
       <c r="E5" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F5" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.18324022743009</v>
+        <v>2.79227653695739</v>
       </c>
       <c r="D6" t="n">
-        <v>16.76305461424021</v>
+        <v>2.723996374814035</v>
       </c>
       <c r="E6" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F6" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.66951053461753</v>
+        <v>0.4337954618753486</v>
       </c>
       <c r="D7" t="n">
-        <v>1.897605759734619</v>
+        <v>0.3083609359568756</v>
       </c>
       <c r="E7" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F7" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.94738180979982</v>
+        <v>2.103949544092471</v>
       </c>
       <c r="D8" t="n">
-        <v>11.70385083859061</v>
+        <v>1.901875761270974</v>
       </c>
       <c r="E8" t="n">
-        <v>9.817875483530795</v>
+        <v>1.595404766073754</v>
       </c>
       <c r="F8" t="n">
-        <v>10.33117775583868</v>
+        <v>1.678816385323785</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
